--- a/docs/res/完整花名册_合并整理.xlsx
+++ b/docs/res/完整花名册_合并整理.xlsx
@@ -5,24 +5,20 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Codex project\1月~6月产能分析\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work_space\agent-driven_gen\docs\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C4502FA-DAC3-4E13-B2ED-E29D703C13A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{122C102B-53BC-4B41-B043-FCD7A2249CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="完整花名册" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">完整花名册!$A$1:$U$195</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -38,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2245" uniqueCount="545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2245" uniqueCount="543">
   <si>
     <t>姓名</t>
   </si>
@@ -1150,9 +1146,6 @@
     <t>王付国</t>
   </si>
   <si>
-    <t>免填</t>
-  </si>
-  <si>
     <t>2015-03-01</t>
   </si>
   <si>
@@ -1246,9 +1239,6 @@
     <t>苏伊潼</t>
   </si>
   <si>
-    <t>预入场</t>
-  </si>
-  <si>
     <t>2026-07-15</t>
   </si>
   <si>
@@ -1519,16 +1509,10 @@
     <t>陈鹏</t>
   </si>
   <si>
-    <t>;别名:大陈鹏</t>
-  </si>
-  <si>
     <t>2018-06-01</t>
   </si>
   <si>
     <t>陈鹏CP</t>
-  </si>
-  <si>
-    <t>工时系统别名:陈鹏CP;别名:小陈鹏;别名:陈鹏;别名:陈鹏CP</t>
   </si>
   <si>
     <t>韦莉琦</t>
@@ -1691,6 +1675,14 @@
   </si>
   <si>
     <t>流造产品规划组</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>工时明细里对应填报部门是智能体研发组的陈鹏</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>工时明细里对应填报部门是境知产品部的陈鹏</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1863,1847 +1855,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="花名册"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="1">
-          <cell r="A1" t="str">
-            <v>姓名</v>
-          </cell>
-          <cell r="E1" t="str">
-            <v>二级部门</v>
-          </cell>
-          <cell r="F1" t="str">
-            <v>三级部门</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="A2" t="str">
-            <v>杨建宏</v>
-          </cell>
-          <cell r="E2" t="str">
-            <v>研发治理部</v>
-          </cell>
-          <cell r="F2" t="str">
-            <v>三快支持组</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3" t="str">
-            <v>蔡俊</v>
-          </cell>
-          <cell r="E3" t="str">
-            <v>研发治理部</v>
-          </cell>
-          <cell r="F3" t="str">
-            <v>配置管理组</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4" t="str">
-            <v>吴良喜</v>
-          </cell>
-          <cell r="E4" t="str">
-            <v>研发治理部</v>
-          </cell>
-          <cell r="F4" t="str">
-            <v>配置管理组</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5" t="str">
-            <v>黄永超</v>
-          </cell>
-          <cell r="E5" t="str">
-            <v>应用产品部</v>
-          </cell>
-          <cell r="F5" t="str">
-            <v>ISV＆集成研发组</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6" t="str">
-            <v>王亮</v>
-          </cell>
-          <cell r="E6" t="str">
-            <v>研发治理部</v>
-          </cell>
-          <cell r="F6" t="str">
-            <v>效能提升组</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7" t="str">
-            <v>曹映辉</v>
-          </cell>
-          <cell r="E7" t="str">
-            <v>流造产品部</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8" t="str">
-            <v>洪泽铨</v>
-          </cell>
-          <cell r="E8" t="str">
-            <v>流造产品部</v>
-          </cell>
-          <cell r="F8" t="str">
-            <v>凌造研发组</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9" t="str">
-            <v>黄伟强</v>
-          </cell>
-          <cell r="E9" t="str">
-            <v>流造产品部</v>
-          </cell>
-          <cell r="F9" t="str">
-            <v>智能体研发组</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10" t="str">
-            <v>施东荣</v>
-          </cell>
-          <cell r="E10" t="str">
-            <v>境知产品部</v>
-          </cell>
-          <cell r="F10" t="str">
-            <v>凌境研发组</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11" t="str">
-            <v>张岩</v>
-          </cell>
-          <cell r="E11" t="str">
-            <v>境知产品部</v>
-          </cell>
-          <cell r="F11" t="str">
-            <v>凌境研发组</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12" t="str">
-            <v>王兵</v>
-          </cell>
-          <cell r="E12" t="str">
-            <v>应用产品部</v>
-          </cell>
-          <cell r="F12" t="str">
-            <v>ISV＆集成研发组</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13" t="str">
-            <v>孙远木</v>
-          </cell>
-          <cell r="E13" t="str">
-            <v>研发治理部</v>
-          </cell>
-          <cell r="F13" t="str">
-            <v>测试部</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14" t="str">
-            <v>谢科明</v>
-          </cell>
-          <cell r="E14" t="str">
-            <v>境知产品部</v>
-          </cell>
-          <cell r="F14" t="str">
-            <v>凌境研发组</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15" t="str">
-            <v>谢星星</v>
-          </cell>
-          <cell r="E15" t="str">
-            <v>应用产品部</v>
-          </cell>
-          <cell r="F15" t="str">
-            <v>ISV＆集成研发组</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16" t="str">
-            <v>陈建林</v>
-          </cell>
-          <cell r="E16" t="str">
-            <v>境知产品部</v>
-          </cell>
-          <cell r="F16" t="str">
-            <v>凌境研发组</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="A17" t="str">
-            <v>吴婉琳</v>
-          </cell>
-          <cell r="E17" t="str">
-            <v>流造产品部</v>
-          </cell>
-          <cell r="F17" t="str">
-            <v>流造产品规划组</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="A18" t="str">
-            <v>范月明</v>
-          </cell>
-          <cell r="E18" t="str">
-            <v>境知产品部</v>
-          </cell>
-          <cell r="F18" t="str">
-            <v>客户成功支持组</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="A19" t="str">
-            <v>周梓凡</v>
-          </cell>
-          <cell r="E19" t="str">
-            <v>流造产品部</v>
-          </cell>
-          <cell r="F19" t="str">
-            <v>智能体研发组</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="A20" t="str">
-            <v>程继军</v>
-          </cell>
-          <cell r="E20" t="str">
-            <v>凌脑创新部</v>
-          </cell>
-          <cell r="F20" t="str">
-            <v>凌脑研发组</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="A21" t="str">
-            <v>林秀贤</v>
-          </cell>
-          <cell r="E21" t="str">
-            <v>境知产品部</v>
-          </cell>
-          <cell r="F21" t="str">
-            <v>凌知研发组</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="A22" t="str">
-            <v>郑献冲</v>
-          </cell>
-          <cell r="E22" t="str">
-            <v>境知产品部</v>
-          </cell>
-          <cell r="F22" t="str">
-            <v>境知产品规划组</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="A23" t="str">
-            <v>曾小兵</v>
-          </cell>
-          <cell r="E23" t="str">
-            <v>研发治理部</v>
-          </cell>
-          <cell r="F23" t="str">
-            <v>测试部</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="A24" t="str">
-            <v>林彬彬</v>
-          </cell>
-          <cell r="E24" t="str">
-            <v>流造产品部</v>
-          </cell>
-          <cell r="F24" t="str">
-            <v>凌流研发组</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="A25" t="str">
-            <v>潘永辉</v>
-          </cell>
-          <cell r="E25" t="str">
-            <v>应用产品部</v>
-          </cell>
-          <cell r="F25" t="str">
-            <v>OA产品研发组</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="A26" t="str">
-            <v>严明镜</v>
-          </cell>
-          <cell r="E26" t="str">
-            <v>流造产品部</v>
-          </cell>
-          <cell r="F26" t="str">
-            <v>凌造研发组</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="A27" t="str">
-            <v>唐小玉</v>
-          </cell>
-          <cell r="E27" t="str">
-            <v>流造产品部</v>
-          </cell>
-          <cell r="F27" t="str">
-            <v>流造产品规划组</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="A28" t="str">
-            <v>封海石</v>
-          </cell>
-          <cell r="E28" t="str">
-            <v>境知产品部</v>
-          </cell>
-          <cell r="F28" t="str">
-            <v>凌境研发组</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="A29" t="str">
-            <v>孟雪峰</v>
-          </cell>
-          <cell r="E29" t="str">
-            <v>研发治理部</v>
-          </cell>
-          <cell r="F29" t="str">
-            <v>配置管理组</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="A30" t="str">
-            <v>代家宽</v>
-          </cell>
-          <cell r="E30" t="str">
-            <v>境知产品部</v>
-          </cell>
-          <cell r="F30" t="str">
-            <v>凌知研发组</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="A31" t="str">
-            <v>余小冬</v>
-          </cell>
-          <cell r="E31" t="str">
-            <v>研发治理部</v>
-          </cell>
-          <cell r="F31" t="str">
-            <v>测试部</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="A32" t="str">
-            <v>张建忠</v>
-          </cell>
-          <cell r="E32" t="str">
-            <v>应用产品部</v>
-          </cell>
-          <cell r="F32" t="str">
-            <v>ISV＆集成研发组</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="A33" t="str">
-            <v>王逍</v>
-          </cell>
-          <cell r="E33" t="str">
-            <v>应用产品部</v>
-          </cell>
-          <cell r="F33" t="str">
-            <v>OA产品研发组</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="A34" t="str">
-            <v>叶正平</v>
-          </cell>
-          <cell r="E34" t="str">
-            <v>应用产品部</v>
-          </cell>
-          <cell r="F34" t="str">
-            <v>OA产品研发组</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="A35" t="str">
-            <v>袁汉祥</v>
-          </cell>
-          <cell r="E35" t="str">
-            <v>流造产品部</v>
-          </cell>
-          <cell r="F35" t="str">
-            <v>凌造研发组</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="A36" t="str">
-            <v>陈鹏_境知</v>
-          </cell>
-          <cell r="E36" t="str">
-            <v>境知产品部</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="A37" t="str">
-            <v>严海星</v>
-          </cell>
-          <cell r="E37" t="str">
-            <v>凌脑创新部</v>
-          </cell>
-          <cell r="F37" t="str">
-            <v>凌脑研发组</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="A38" t="str">
-            <v>杨铮</v>
-          </cell>
-          <cell r="E38" t="str">
-            <v>凌脑创新部</v>
-          </cell>
-          <cell r="F38" t="str">
-            <v>凌脑研发组</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="A39" t="str">
-            <v>谢宇冶</v>
-          </cell>
-          <cell r="E39" t="str">
-            <v>研发治理部</v>
-          </cell>
-          <cell r="F39" t="str">
-            <v>测试部</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="A40" t="str">
-            <v>官晓林</v>
-          </cell>
-          <cell r="E40" t="str">
-            <v>境知产品部</v>
-          </cell>
-          <cell r="F40" t="str">
-            <v>客户成功支持组</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="A41" t="str">
-            <v>马风英</v>
-          </cell>
-          <cell r="E41" t="str">
-            <v>研发治理部</v>
-          </cell>
-          <cell r="F41" t="str">
-            <v>测试部</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="A42" t="str">
-            <v>邓春喜</v>
-          </cell>
-          <cell r="E42" t="str">
-            <v>应用产品部</v>
-          </cell>
-          <cell r="F42" t="str">
-            <v>应用产品规划组</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="A43" t="str">
-            <v>谭昌香</v>
-          </cell>
-          <cell r="E43" t="str">
-            <v>应用产品部</v>
-          </cell>
-          <cell r="F43" t="str">
-            <v>OA产品研发组</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="A44" t="str">
-            <v>张艳</v>
-          </cell>
-          <cell r="E44" t="str">
-            <v>境知产品部</v>
-          </cell>
-          <cell r="F44" t="str">
-            <v>境知产品规划组</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="A45" t="str">
-            <v>许远周</v>
-          </cell>
-          <cell r="E45" t="str">
-            <v>境知产品部</v>
-          </cell>
-          <cell r="F45" t="str">
-            <v>凌知研发组</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="A46" t="str">
-            <v>洪健</v>
-          </cell>
-          <cell r="E46" t="str">
-            <v>应用产品部</v>
-          </cell>
-          <cell r="F46" t="str">
-            <v>OA产品研发组</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="A47" t="str">
-            <v>张越良</v>
-          </cell>
-          <cell r="E47" t="str">
-            <v>流造产品部</v>
-          </cell>
-          <cell r="F47" t="str">
-            <v>智能体研发组</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="A48" t="str">
-            <v>欧宇</v>
-          </cell>
-          <cell r="E48" t="str">
-            <v>应用产品部</v>
-          </cell>
-          <cell r="F48" t="str">
-            <v>OA产品研发组</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="A49" t="str">
-            <v>陈正坤</v>
-          </cell>
-          <cell r="E49" t="str">
-            <v>应用产品部</v>
-          </cell>
-          <cell r="F49" t="str">
-            <v>ISV＆集成研发组</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="A50" t="str">
-            <v>李尚志</v>
-          </cell>
-          <cell r="E50" t="str">
-            <v>流造产品部</v>
-          </cell>
-          <cell r="F50" t="str">
-            <v>凌造研发组</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="A51" t="str">
-            <v>余亮</v>
-          </cell>
-          <cell r="E51" t="str">
-            <v>流造产品部</v>
-          </cell>
-          <cell r="F51" t="str">
-            <v>智能体研发组</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="A52" t="str">
-            <v>周才伟</v>
-          </cell>
-          <cell r="E52" t="str">
-            <v>应用产品部</v>
-          </cell>
-          <cell r="F52" t="str">
-            <v>产品体验组</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="A53" t="str">
-            <v>郑鑫</v>
-          </cell>
-          <cell r="E53" t="str">
-            <v>应用产品部</v>
-          </cell>
-          <cell r="F53" t="str">
-            <v>OA产品研发组</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="A54" t="str">
-            <v>任和珍</v>
-          </cell>
-          <cell r="E54" t="str">
-            <v>流造产品部</v>
-          </cell>
-          <cell r="F54" t="str">
-            <v>流造产品规划组</v>
-          </cell>
-        </row>
-        <row r="55">
-          <cell r="A55" t="str">
-            <v>张锐</v>
-          </cell>
-          <cell r="E55" t="str">
-            <v>流造产品部</v>
-          </cell>
-          <cell r="F55" t="str">
-            <v>凌造研发组</v>
-          </cell>
-        </row>
-        <row r="56">
-          <cell r="A56" t="str">
-            <v>陈火旺</v>
-          </cell>
-          <cell r="E56" t="str">
-            <v>应用产品部</v>
-          </cell>
-          <cell r="F56" t="str">
-            <v>ISV＆集成研发组</v>
-          </cell>
-        </row>
-        <row r="57">
-          <cell r="A57" t="str">
-            <v>刘庞</v>
-          </cell>
-          <cell r="E57" t="str">
-            <v>凌脑创新部</v>
-          </cell>
-          <cell r="F57" t="str">
-            <v>凌脑研发组</v>
-          </cell>
-        </row>
-        <row r="58">
-          <cell r="A58" t="str">
-            <v>郑操辉</v>
-          </cell>
-          <cell r="E58" t="str">
-            <v>应用产品部</v>
-          </cell>
-          <cell r="F58" t="str">
-            <v>OA产品研发组</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="A59" t="str">
-            <v>唐有炜</v>
-          </cell>
-          <cell r="E59" t="str">
-            <v>凌脑创新部</v>
-          </cell>
-          <cell r="F59" t="str">
-            <v>凌脑研发组</v>
-          </cell>
-        </row>
-        <row r="60">
-          <cell r="A60" t="str">
-            <v>童张玉</v>
-          </cell>
-          <cell r="E60" t="str">
-            <v>应用产品部</v>
-          </cell>
-          <cell r="F60" t="str">
-            <v>产品体验组</v>
-          </cell>
-        </row>
-        <row r="61">
-          <cell r="A61" t="str">
-            <v>郑伯宇</v>
-          </cell>
-          <cell r="E61" t="str">
-            <v>研发治理部</v>
-          </cell>
-          <cell r="F61" t="str">
-            <v>效能提升组</v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="A62" t="str">
-            <v>张小雪</v>
-          </cell>
-          <cell r="E62" t="str">
-            <v>研发治理部</v>
-          </cell>
-          <cell r="F62" t="str">
-            <v>测试部</v>
-          </cell>
-        </row>
-        <row r="63">
-          <cell r="A63" t="str">
-            <v>贺双</v>
-          </cell>
-          <cell r="E63" t="str">
-            <v>流造产品部</v>
-          </cell>
-          <cell r="F63" t="str">
-            <v>流造产品规划组</v>
-          </cell>
-        </row>
-        <row r="64">
-          <cell r="A64" t="str">
-            <v>侯晓博</v>
-          </cell>
-          <cell r="E64" t="str">
-            <v>流造产品部</v>
-          </cell>
-          <cell r="F64" t="str">
-            <v>智能体研发组</v>
-          </cell>
-        </row>
-        <row r="65">
-          <cell r="A65" t="str">
-            <v>李芳敏</v>
-          </cell>
-          <cell r="E65" t="str">
-            <v>境知产品部</v>
-          </cell>
-          <cell r="F65" t="str">
-            <v>凌知研发组</v>
-          </cell>
-        </row>
-        <row r="66">
-          <cell r="A66" t="str">
-            <v>刘宏羽</v>
-          </cell>
-          <cell r="E66" t="str">
-            <v>凌脑创新部</v>
-          </cell>
-          <cell r="F66" t="str">
-            <v>凌脑研发组</v>
-          </cell>
-        </row>
-        <row r="67">
-          <cell r="A67" t="str">
-            <v>周勉</v>
-          </cell>
-          <cell r="E67" t="str">
-            <v>境知产品部</v>
-          </cell>
-          <cell r="F67" t="str">
-            <v>凌境研发组</v>
-          </cell>
-        </row>
-        <row r="68">
-          <cell r="A68" t="str">
-            <v>郭敏</v>
-          </cell>
-          <cell r="E68" t="str">
-            <v>凌脑创新部</v>
-          </cell>
-          <cell r="F68" t="str">
-            <v>凌脑研发组</v>
-          </cell>
-        </row>
-        <row r="69">
-          <cell r="A69" t="str">
-            <v>郑裕显</v>
-          </cell>
-          <cell r="E69" t="str">
-            <v>技术架构部</v>
-          </cell>
-        </row>
-        <row r="70">
-          <cell r="A70" t="str">
-            <v>陈鹏_流造</v>
-          </cell>
-          <cell r="E70" t="str">
-            <v>流造产品部</v>
-          </cell>
-          <cell r="F70" t="str">
-            <v>智能体研发组</v>
-          </cell>
-        </row>
-        <row r="71">
-          <cell r="A71" t="str">
-            <v>陈鑫康</v>
-          </cell>
-          <cell r="E71" t="str">
-            <v>应用产品部</v>
-          </cell>
-          <cell r="F71" t="str">
-            <v>OA产品研发组</v>
-          </cell>
-        </row>
-        <row r="72">
-          <cell r="A72" t="str">
-            <v>黄琴</v>
-          </cell>
-          <cell r="E72" t="str">
-            <v>流造产品部</v>
-          </cell>
-          <cell r="F72" t="str">
-            <v>凌造研发组</v>
-          </cell>
-        </row>
-        <row r="73">
-          <cell r="A73" t="str">
-            <v>孙丝语</v>
-          </cell>
-          <cell r="E73" t="str">
-            <v>应用产品部</v>
-          </cell>
-          <cell r="F73" t="str">
-            <v>应用产品规划组</v>
-          </cell>
-        </row>
-        <row r="74">
-          <cell r="A74" t="str">
-            <v>蒋毛生</v>
-          </cell>
-          <cell r="E74" t="str">
-            <v>研发治理部</v>
-          </cell>
-          <cell r="F74" t="str">
-            <v>配置管理组</v>
-          </cell>
-        </row>
-        <row r="75">
-          <cell r="A75" t="str">
-            <v>徐文辉</v>
-          </cell>
-          <cell r="E75" t="str">
-            <v>应用产品部</v>
-          </cell>
-          <cell r="F75" t="str">
-            <v>OA产品研发组</v>
-          </cell>
-        </row>
-        <row r="76">
-          <cell r="A76" t="str">
-            <v>赖嘉怡</v>
-          </cell>
-          <cell r="E76" t="str">
-            <v>流造产品部</v>
-          </cell>
-          <cell r="F76" t="str">
-            <v>流造产品规划组</v>
-          </cell>
-        </row>
-        <row r="77">
-          <cell r="A77" t="str">
-            <v>黎荣森</v>
-          </cell>
-          <cell r="E77" t="str">
-            <v>流造产品部</v>
-          </cell>
-          <cell r="F77" t="str">
-            <v>凌流研发组</v>
-          </cell>
-        </row>
-        <row r="78">
-          <cell r="A78" t="str">
-            <v>韦莉琦</v>
-          </cell>
-          <cell r="E78" t="str">
-            <v>研发治理部</v>
-          </cell>
-          <cell r="F78" t="str">
-            <v>三快支持组</v>
-          </cell>
-        </row>
-        <row r="79">
-          <cell r="A79" t="str">
-            <v>利妙凤</v>
-          </cell>
-          <cell r="E79" t="str">
-            <v>研发治理部</v>
-          </cell>
-          <cell r="F79" t="str">
-            <v>测试部</v>
-          </cell>
-        </row>
-        <row r="80">
-          <cell r="A80" t="str">
-            <v>刘振</v>
-          </cell>
-          <cell r="E80" t="str">
-            <v>境知产品部</v>
-          </cell>
-          <cell r="F80" t="str">
-            <v>凌境研发组</v>
-          </cell>
-        </row>
-        <row r="81">
-          <cell r="A81" t="str">
-            <v>刘芬</v>
-          </cell>
-          <cell r="E81" t="str">
-            <v>研发治理部</v>
-          </cell>
-          <cell r="F81" t="str">
-            <v>测试部</v>
-          </cell>
-        </row>
-        <row r="82">
-          <cell r="A82" t="str">
-            <v>张晓甜</v>
-          </cell>
-          <cell r="E82" t="str">
-            <v>境知产品部</v>
-          </cell>
-          <cell r="F82" t="str">
-            <v>凌境研发组</v>
-          </cell>
-        </row>
-        <row r="83">
-          <cell r="A83" t="str">
-            <v>高木生</v>
-          </cell>
-          <cell r="E83" t="str">
-            <v>流造产品部</v>
-          </cell>
-          <cell r="F83" t="str">
-            <v>凌流研发组</v>
-          </cell>
-        </row>
-        <row r="84">
-          <cell r="A84" t="str">
-            <v>马彦研</v>
-          </cell>
-          <cell r="E84" t="str">
-            <v>应用产品部</v>
-          </cell>
-          <cell r="F84" t="str">
-            <v>ISV＆集成研发组</v>
-          </cell>
-        </row>
-        <row r="85">
-          <cell r="A85" t="str">
-            <v>帅胜余</v>
-          </cell>
-          <cell r="E85" t="str">
-            <v>流造产品部</v>
-          </cell>
-          <cell r="F85" t="str">
-            <v>流造产品规划组</v>
-          </cell>
-        </row>
-        <row r="86">
-          <cell r="A86" t="str">
-            <v>陈丹萍</v>
-          </cell>
-          <cell r="E86" t="str">
-            <v>应用产品部</v>
-          </cell>
-          <cell r="F86" t="str">
-            <v>ISV＆集成研发组</v>
-          </cell>
-        </row>
-        <row r="87">
-          <cell r="A87" t="str">
-            <v>唐程润</v>
-          </cell>
-          <cell r="E87" t="str">
-            <v>应用产品部</v>
-          </cell>
-          <cell r="F87" t="str">
-            <v>OA产品研发组</v>
-          </cell>
-        </row>
-        <row r="88">
-          <cell r="A88" t="str">
-            <v>陆金兰</v>
-          </cell>
-          <cell r="E88" t="str">
-            <v>研发治理部</v>
-          </cell>
-          <cell r="F88" t="str">
-            <v>测试部</v>
-          </cell>
-        </row>
-        <row r="89">
-          <cell r="A89" t="str">
-            <v>汪亮</v>
-          </cell>
-          <cell r="E89" t="str">
-            <v>应用产品部</v>
-          </cell>
-          <cell r="F89" t="str">
-            <v>OA产品研发组</v>
-          </cell>
-        </row>
-        <row r="90">
-          <cell r="A90" t="str">
-            <v>余家安</v>
-          </cell>
-          <cell r="E90" t="str">
-            <v>流造产品部</v>
-          </cell>
-          <cell r="F90" t="str">
-            <v>凌流研发组</v>
-          </cell>
-        </row>
-        <row r="91">
-          <cell r="A91" t="str">
-            <v>姚宇</v>
-          </cell>
-          <cell r="E91" t="str">
-            <v>凌脑创新部</v>
-          </cell>
-          <cell r="F91" t="str">
-            <v>凌脑研发组</v>
-          </cell>
-        </row>
-        <row r="92">
-          <cell r="A92" t="str">
-            <v>刘萍</v>
-          </cell>
-          <cell r="E92" t="str">
-            <v>产研办公室</v>
-          </cell>
-        </row>
-        <row r="93">
-          <cell r="A93" t="str">
-            <v>赵荧莹</v>
-          </cell>
-          <cell r="E93" t="str">
-            <v>境知产品部</v>
-          </cell>
-          <cell r="F93" t="str">
-            <v>境知产品规划组</v>
-          </cell>
-        </row>
-        <row r="94">
-          <cell r="A94" t="str">
-            <v>顾凌斐</v>
-          </cell>
-          <cell r="E94" t="str">
-            <v>应用产品部</v>
-          </cell>
-          <cell r="F94" t="str">
-            <v>产品体验组</v>
-          </cell>
-        </row>
-        <row r="95">
-          <cell r="A95" t="str">
-            <v>付文松</v>
-          </cell>
-          <cell r="E95" t="str">
-            <v>流造产品部</v>
-          </cell>
-          <cell r="F95" t="str">
-            <v>智能体研发组</v>
-          </cell>
-        </row>
-        <row r="96">
-          <cell r="A96" t="str">
-            <v>王丽永</v>
-          </cell>
-          <cell r="E96" t="str">
-            <v>凌脑创新部</v>
-          </cell>
-          <cell r="F96" t="str">
-            <v>凌脑研发组</v>
-          </cell>
-        </row>
-        <row r="97">
-          <cell r="A97" t="str">
-            <v>吴彬</v>
-          </cell>
-          <cell r="E97" t="str">
-            <v>研发治理部</v>
-          </cell>
-          <cell r="F97" t="str">
-            <v>效能提升组</v>
-          </cell>
-        </row>
-        <row r="98">
-          <cell r="A98" t="str">
-            <v>张颖</v>
-          </cell>
-          <cell r="E98" t="str">
-            <v>境知产品部</v>
-          </cell>
-          <cell r="F98" t="str">
-            <v>凌知研发组</v>
-          </cell>
-        </row>
-        <row r="99">
-          <cell r="A99" t="str">
-            <v>罗永艺</v>
-          </cell>
-          <cell r="E99" t="str">
-            <v>研发治理部</v>
-          </cell>
-          <cell r="F99" t="str">
-            <v>测试部</v>
-          </cell>
-        </row>
-        <row r="100">
-          <cell r="A100" t="str">
-            <v>刘银</v>
-          </cell>
-          <cell r="E100" t="str">
-            <v>研发治理部</v>
-          </cell>
-          <cell r="F100" t="str">
-            <v>测试部</v>
-          </cell>
-        </row>
-        <row r="101">
-          <cell r="A101" t="str">
-            <v>潘浩丹</v>
-          </cell>
-          <cell r="E101" t="str">
-            <v>应用产品部</v>
-          </cell>
-          <cell r="F101" t="str">
-            <v>产品体验组</v>
-          </cell>
-        </row>
-        <row r="102">
-          <cell r="A102" t="str">
-            <v>陈浩</v>
-          </cell>
-          <cell r="E102" t="str">
-            <v>应用产品部</v>
-          </cell>
-          <cell r="F102" t="str">
-            <v>ISV＆集成研发组</v>
-          </cell>
-        </row>
-        <row r="103">
-          <cell r="A103" t="str">
-            <v>李海瑞</v>
-          </cell>
-          <cell r="E103" t="str">
-            <v>应用产品部</v>
-          </cell>
-          <cell r="F103" t="str">
-            <v>应用产品规划组</v>
-          </cell>
-        </row>
-        <row r="104">
-          <cell r="A104" t="str">
-            <v>李炜健</v>
-          </cell>
-          <cell r="E104" t="str">
-            <v>境知产品部</v>
-          </cell>
-          <cell r="F104" t="str">
-            <v>境知产品规划组</v>
-          </cell>
-        </row>
-        <row r="105">
-          <cell r="A105" t="str">
-            <v>刘水明</v>
-          </cell>
-          <cell r="E105" t="str">
-            <v>应用产品部</v>
-          </cell>
-          <cell r="F105" t="str">
-            <v>OA产品研发组</v>
-          </cell>
-        </row>
-        <row r="106">
-          <cell r="A106" t="str">
-            <v>李琦</v>
-          </cell>
-          <cell r="E106" t="str">
-            <v>研发治理部</v>
-          </cell>
-          <cell r="F106" t="str">
-            <v>测试部</v>
-          </cell>
-        </row>
-        <row r="107">
-          <cell r="A107" t="str">
-            <v>张志江</v>
-          </cell>
-          <cell r="E107" t="str">
-            <v>流造产品部</v>
-          </cell>
-          <cell r="F107" t="str">
-            <v>凌造研发组</v>
-          </cell>
-        </row>
-        <row r="108">
-          <cell r="A108" t="str">
-            <v>刘娜</v>
-          </cell>
-          <cell r="E108" t="str">
-            <v>应用产品部</v>
-          </cell>
-          <cell r="F108" t="str">
-            <v>ISV＆集成研发组</v>
-          </cell>
-        </row>
-        <row r="109">
-          <cell r="A109" t="str">
-            <v>张慧珍</v>
-          </cell>
-          <cell r="E109" t="str">
-            <v>产研办公室</v>
-          </cell>
-        </row>
-        <row r="110">
-          <cell r="A110" t="str">
-            <v>叶冠华</v>
-          </cell>
-          <cell r="E110" t="str">
-            <v>境知产品部</v>
-          </cell>
-          <cell r="F110" t="str">
-            <v>客户成功支持组</v>
-          </cell>
-        </row>
-        <row r="111">
-          <cell r="A111" t="str">
-            <v>潘在昌</v>
-          </cell>
-          <cell r="E111" t="str">
-            <v>境知产品部</v>
-          </cell>
-          <cell r="F111" t="str">
-            <v>境知产品规划组</v>
-          </cell>
-        </row>
-        <row r="112">
-          <cell r="A112" t="str">
-            <v>李博宇</v>
-          </cell>
-          <cell r="E112" t="str">
-            <v>应用产品部</v>
-          </cell>
-          <cell r="F112" t="str">
-            <v>产品体验组</v>
-          </cell>
-        </row>
-        <row r="113">
-          <cell r="A113" t="str">
-            <v>梁明达</v>
-          </cell>
-          <cell r="E113" t="str">
-            <v>流造产品部</v>
-          </cell>
-          <cell r="F113" t="str">
-            <v>凌流研发组</v>
-          </cell>
-        </row>
-        <row r="114">
-          <cell r="A114" t="str">
-            <v>吴世佳</v>
-          </cell>
-          <cell r="E114" t="str">
-            <v>应用产品部</v>
-          </cell>
-          <cell r="F114" t="str">
-            <v>应用产品规划组</v>
-          </cell>
-        </row>
-        <row r="115">
-          <cell r="A115" t="str">
-            <v>卢海强</v>
-          </cell>
-          <cell r="E115" t="str">
-            <v>流造产品部</v>
-          </cell>
-          <cell r="F115" t="str">
-            <v>智能体研发组</v>
-          </cell>
-        </row>
-        <row r="116">
-          <cell r="A116" t="str">
-            <v>朱朋祥</v>
-          </cell>
-          <cell r="E116" t="str">
-            <v>应用产品部</v>
-          </cell>
-          <cell r="F116" t="str">
-            <v>OA产品研发组</v>
-          </cell>
-        </row>
-        <row r="117">
-          <cell r="A117" t="str">
-            <v>蒋业旺</v>
-          </cell>
-          <cell r="E117" t="str">
-            <v>应用产品部</v>
-          </cell>
-          <cell r="F117" t="str">
-            <v>ISV＆集成研发组</v>
-          </cell>
-        </row>
-        <row r="118">
-          <cell r="A118" t="str">
-            <v>林勤耀</v>
-          </cell>
-          <cell r="E118" t="str">
-            <v>研发治理部</v>
-          </cell>
-          <cell r="F118" t="str">
-            <v>测试部</v>
-          </cell>
-        </row>
-        <row r="119">
-          <cell r="A119" t="str">
-            <v>程默</v>
-          </cell>
-          <cell r="E119" t="str">
-            <v>凌脑创新部</v>
-          </cell>
-          <cell r="F119" t="str">
-            <v>凌脑研发组</v>
-          </cell>
-        </row>
-        <row r="120">
-          <cell r="A120" t="str">
-            <v>王彪</v>
-          </cell>
-          <cell r="E120" t="str">
-            <v>流造产品部</v>
-          </cell>
-          <cell r="F120" t="str">
-            <v>凌造研发组</v>
-          </cell>
-        </row>
-        <row r="121">
-          <cell r="A121" t="str">
-            <v>凌通</v>
-          </cell>
-          <cell r="E121" t="str">
-            <v>流造产品部</v>
-          </cell>
-          <cell r="F121" t="str">
-            <v>凌造研发组</v>
-          </cell>
-        </row>
-        <row r="122">
-          <cell r="A122" t="str">
-            <v>蔡海练</v>
-          </cell>
-          <cell r="E122" t="str">
-            <v>应用产品部</v>
-          </cell>
-          <cell r="F122" t="str">
-            <v>OA产品研发组</v>
-          </cell>
-        </row>
-        <row r="123">
-          <cell r="A123" t="str">
-            <v>李昂</v>
-          </cell>
-          <cell r="E123" t="str">
-            <v>境知产品部</v>
-          </cell>
-          <cell r="F123" t="str">
-            <v>凌知研发组</v>
-          </cell>
-        </row>
-        <row r="124">
-          <cell r="A124" t="str">
-            <v>熊金华</v>
-          </cell>
-          <cell r="E124" t="str">
-            <v>应用产品部</v>
-          </cell>
-          <cell r="F124" t="str">
-            <v>ISV＆集成研发组</v>
-          </cell>
-        </row>
-        <row r="125">
-          <cell r="A125" t="str">
-            <v>潘钜</v>
-          </cell>
-          <cell r="E125" t="str">
-            <v>流造产品部</v>
-          </cell>
-          <cell r="F125" t="str">
-            <v>凌流研发组</v>
-          </cell>
-        </row>
-        <row r="126">
-          <cell r="A126" t="str">
-            <v>张艳萍</v>
-          </cell>
-          <cell r="E126" t="str">
-            <v>研发治理部</v>
-          </cell>
-          <cell r="F126" t="str">
-            <v>测试部</v>
-          </cell>
-        </row>
-        <row r="127">
-          <cell r="A127" t="str">
-            <v>廖星</v>
-          </cell>
-          <cell r="E127" t="str">
-            <v>流造产品部</v>
-          </cell>
-          <cell r="F127" t="str">
-            <v>凌造研发组</v>
-          </cell>
-        </row>
-        <row r="128">
-          <cell r="A128" t="str">
-            <v>王路平</v>
-          </cell>
-          <cell r="E128" t="str">
-            <v>境知产品部</v>
-          </cell>
-          <cell r="F128" t="str">
-            <v>客户成功支持组</v>
-          </cell>
-        </row>
-        <row r="129">
-          <cell r="A129" t="str">
-            <v>潘珏</v>
-          </cell>
-          <cell r="E129" t="str">
-            <v>凌脑创新部</v>
-          </cell>
-          <cell r="F129" t="str">
-            <v>凌脑产品规划组</v>
-          </cell>
-        </row>
-        <row r="130">
-          <cell r="A130" t="str">
-            <v>廖嘉琪</v>
-          </cell>
-          <cell r="E130" t="str">
-            <v>流造产品部</v>
-          </cell>
-          <cell r="F130" t="str">
-            <v>流造产品规划组</v>
-          </cell>
-        </row>
-        <row r="131">
-          <cell r="A131" t="str">
-            <v>胡真毓</v>
-          </cell>
-          <cell r="E131" t="str">
-            <v>凌脑创新部</v>
-          </cell>
-          <cell r="F131" t="str">
-            <v>凌脑产品规划组</v>
-          </cell>
-        </row>
-        <row r="132">
-          <cell r="A132" t="str">
-            <v>李继维</v>
-          </cell>
-          <cell r="E132" t="str">
-            <v>凌脑创新部</v>
-          </cell>
-          <cell r="F132" t="str">
-            <v>凌脑研发组</v>
-          </cell>
-        </row>
-        <row r="133">
-          <cell r="A133" t="str">
-            <v>李志强</v>
-          </cell>
-          <cell r="E133" t="str">
-            <v>凌脑创新部</v>
-          </cell>
-          <cell r="F133" t="str">
-            <v>凌脑研发组</v>
-          </cell>
-        </row>
-        <row r="134">
-          <cell r="A134" t="str">
-            <v>徐伟雄</v>
-          </cell>
-          <cell r="E134" t="str">
-            <v>技术架构部</v>
-          </cell>
-        </row>
-        <row r="135">
-          <cell r="A135" t="str">
-            <v>方楠</v>
-          </cell>
-          <cell r="E135" t="str">
-            <v>技术架构部</v>
-          </cell>
-        </row>
-        <row r="136">
-          <cell r="A136" t="str">
-            <v>杨胜</v>
-          </cell>
-          <cell r="E136" t="str">
-            <v>流造产品部</v>
-          </cell>
-          <cell r="F136" t="str">
-            <v>智能体研发组</v>
-          </cell>
-        </row>
-        <row r="137">
-          <cell r="A137" t="str">
-            <v>严冰</v>
-          </cell>
-          <cell r="E137" t="str">
-            <v>产研办公室</v>
-          </cell>
-        </row>
-        <row r="138">
-          <cell r="A138" t="str">
-            <v>李夏昕</v>
-          </cell>
-          <cell r="E138" t="str">
-            <v>产研办公室</v>
-          </cell>
-        </row>
-        <row r="139">
-          <cell r="A139" t="str">
-            <v>周昱岑</v>
-          </cell>
-          <cell r="E139" t="str">
-            <v>境知产品部</v>
-          </cell>
-          <cell r="F139" t="str">
-            <v>客户成功支持组</v>
-          </cell>
-        </row>
-        <row r="140">
-          <cell r="A140" t="str">
-            <v>李俊</v>
-          </cell>
-          <cell r="E140" t="str">
-            <v>境知产品部</v>
-          </cell>
-          <cell r="F140" t="str">
-            <v>客户成功支持组</v>
-          </cell>
-        </row>
-        <row r="141">
-          <cell r="A141" t="str">
-            <v>陈增乐</v>
-          </cell>
-          <cell r="E141" t="str">
-            <v>研发治理部</v>
-          </cell>
-          <cell r="F141" t="str">
-            <v>测试部</v>
-          </cell>
-        </row>
-        <row r="142">
-          <cell r="A142" t="str">
-            <v>崔胜兰</v>
-          </cell>
-          <cell r="E142" t="str">
-            <v>研发治理部</v>
-          </cell>
-          <cell r="F142" t="str">
-            <v>测试部</v>
-          </cell>
-        </row>
-        <row r="143">
-          <cell r="A143" t="str">
-            <v>管思雅</v>
-          </cell>
-          <cell r="E143" t="str">
-            <v>产研办公室</v>
-          </cell>
-        </row>
-        <row r="144">
-          <cell r="A144" t="str">
-            <v>徐颖</v>
-          </cell>
-          <cell r="E144" t="str">
-            <v>产研办公室</v>
-          </cell>
-        </row>
-        <row r="145">
-          <cell r="A145" t="str">
-            <v>伍跳</v>
-          </cell>
-          <cell r="E145" t="str">
-            <v>外包</v>
-          </cell>
-          <cell r="F145" t="str">
-            <v>外包</v>
-          </cell>
-        </row>
-        <row r="146">
-          <cell r="A146" t="str">
-            <v>林锦春</v>
-          </cell>
-          <cell r="E146" t="str">
-            <v>外包</v>
-          </cell>
-          <cell r="F146" t="str">
-            <v>外包</v>
-          </cell>
-        </row>
-        <row r="147">
-          <cell r="A147" t="str">
-            <v>谯云峰</v>
-          </cell>
-          <cell r="E147" t="str">
-            <v>外包</v>
-          </cell>
-          <cell r="F147" t="str">
-            <v>外包</v>
-          </cell>
-        </row>
-        <row r="148">
-          <cell r="A148" t="str">
-            <v>肖胜文</v>
-          </cell>
-          <cell r="E148" t="str">
-            <v>外包</v>
-          </cell>
-          <cell r="F148" t="str">
-            <v>外包</v>
-          </cell>
-        </row>
-        <row r="149">
-          <cell r="A149" t="str">
-            <v>葛志聪</v>
-          </cell>
-          <cell r="E149" t="str">
-            <v>外包</v>
-          </cell>
-          <cell r="F149" t="str">
-            <v>外包</v>
-          </cell>
-        </row>
-        <row r="150">
-          <cell r="A150" t="str">
-            <v>刘浩鹏</v>
-          </cell>
-          <cell r="E150" t="str">
-            <v>外包</v>
-          </cell>
-          <cell r="F150" t="str">
-            <v>外包</v>
-          </cell>
-        </row>
-        <row r="151">
-          <cell r="A151" t="str">
-            <v>凯颖</v>
-          </cell>
-          <cell r="E151" t="str">
-            <v>外包</v>
-          </cell>
-          <cell r="F151" t="str">
-            <v>外包</v>
-          </cell>
-        </row>
-        <row r="152">
-          <cell r="A152" t="str">
-            <v>王鼎</v>
-          </cell>
-          <cell r="E152" t="str">
-            <v>外包</v>
-          </cell>
-          <cell r="F152" t="str">
-            <v>外包</v>
-          </cell>
-        </row>
-        <row r="153">
-          <cell r="A153" t="str">
-            <v>彭雷</v>
-          </cell>
-          <cell r="E153" t="str">
-            <v>外包</v>
-          </cell>
-          <cell r="F153" t="str">
-            <v>外包</v>
-          </cell>
-        </row>
-        <row r="154">
-          <cell r="A154" t="str">
-            <v>冯锦秋</v>
-          </cell>
-          <cell r="E154" t="str">
-            <v>外包</v>
-          </cell>
-          <cell r="F154" t="str">
-            <v>外包</v>
-          </cell>
-        </row>
-        <row r="155">
-          <cell r="A155" t="str">
-            <v>高逸晨</v>
-          </cell>
-          <cell r="E155" t="str">
-            <v>外包</v>
-          </cell>
-          <cell r="F155" t="str">
-            <v>外包</v>
-          </cell>
-        </row>
-        <row r="156">
-          <cell r="A156" t="str">
-            <v>钟丽婷</v>
-          </cell>
-          <cell r="E156" t="str">
-            <v>外包</v>
-          </cell>
-          <cell r="F156" t="str">
-            <v>外包</v>
-          </cell>
-        </row>
-        <row r="157">
-          <cell r="A157" t="str">
-            <v>谢幸</v>
-          </cell>
-          <cell r="E157" t="str">
-            <v>产研办公室</v>
-          </cell>
-        </row>
-        <row r="158">
-          <cell r="A158" t="str">
-            <v>杨旭晋</v>
-          </cell>
-        </row>
-        <row r="159">
-          <cell r="A159" t="str">
-            <v>熊浪</v>
-          </cell>
-          <cell r="E159" t="str">
-            <v>华南业务一部</v>
-          </cell>
-        </row>
-        <row r="160">
-          <cell r="A160" t="str">
-            <v>李雪辉</v>
-          </cell>
-          <cell r="E160" t="str">
-            <v>华南开发一组</v>
-          </cell>
-        </row>
-        <row r="161">
-          <cell r="A161" t="str">
-            <v>黄溢</v>
-          </cell>
-          <cell r="E161" t="str">
-            <v>华南开发一组</v>
-          </cell>
-        </row>
-        <row r="162">
-          <cell r="A162" t="str">
-            <v>陈婷婷</v>
-          </cell>
-          <cell r="E162" t="str">
-            <v>智能中台规划部</v>
-          </cell>
-        </row>
-        <row r="163">
-          <cell r="A163" t="str">
-            <v>龚浩</v>
-          </cell>
-          <cell r="E163" t="str">
-            <v>BPM组</v>
-          </cell>
-        </row>
-        <row r="164">
-          <cell r="A164" t="str">
-            <v>郑晓婷</v>
-          </cell>
-          <cell r="E164" t="str">
-            <v>EKP18产品研发部</v>
-          </cell>
-        </row>
-        <row r="165">
-          <cell r="A165" t="str">
-            <v>梁梓轩</v>
-          </cell>
-          <cell r="E165" t="str">
-            <v>智能中台测试组</v>
-          </cell>
-        </row>
-        <row r="166">
-          <cell r="A166" t="str">
-            <v>谢微</v>
-          </cell>
-          <cell r="E166" t="str">
-            <v>产研办公室</v>
-          </cell>
-        </row>
-        <row r="167">
-          <cell r="A167" t="str">
-            <v>杨太双</v>
-          </cell>
-          <cell r="E167" t="str">
-            <v>智能中台体验组</v>
-          </cell>
-        </row>
-        <row r="168">
-          <cell r="A168" t="str">
-            <v>刘水生</v>
-          </cell>
-          <cell r="E168" t="str">
-            <v>EKP18产品研发部</v>
-          </cell>
-        </row>
-        <row r="169">
-          <cell r="A169" t="str">
-            <v>屈高鹏</v>
-          </cell>
-          <cell r="E169" t="str">
-            <v>产品研发中心</v>
-          </cell>
-        </row>
-        <row r="170">
-          <cell r="A170" t="str">
-            <v>李嘉祥</v>
-          </cell>
-          <cell r="E170" t="str">
-            <v>KK组</v>
-          </cell>
-        </row>
-        <row r="171">
-          <cell r="A171" t="str">
-            <v>刘继想</v>
-          </cell>
-          <cell r="E171" t="str">
-            <v>数据中台研发部</v>
-          </cell>
-        </row>
-        <row r="172">
-          <cell r="A172" t="str">
-            <v>彭冯</v>
-          </cell>
-          <cell r="E172" t="str">
-            <v>用户运营组</v>
-          </cell>
-        </row>
-        <row r="173">
-          <cell r="A173" t="str">
-            <v>陈栋</v>
-          </cell>
-          <cell r="E173" t="str">
-            <v>治理&amp;算法组</v>
-          </cell>
-        </row>
-        <row r="174">
-          <cell r="A174" t="str">
-            <v>邱淏辰</v>
-          </cell>
-          <cell r="E174" t="str">
-            <v>凌脑研发组</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3992,20 +2143,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:W195"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:U195"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="19.875" customWidth="1"/>
+    <col min="4" max="4" width="19.90625" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
     <col min="6" max="6" width="21" customWidth="1"/>
-    <col min="8" max="8" width="18.5" customWidth="1"/>
+    <col min="8" max="8" width="18.453125" customWidth="1"/>
     <col min="10" max="14" width="0" hidden="1" customWidth="1"/>
-    <col min="19" max="19" width="15.125" customWidth="1"/>
-    <col min="20" max="20" width="16.75" customWidth="1"/>
-    <col min="22" max="22" width="24.125" customWidth="1"/>
+    <col min="15" max="15" width="53.6328125" customWidth="1"/>
+    <col min="19" max="19" width="15.08984375" customWidth="1"/>
+    <col min="20" max="20" width="16.7265625" customWidth="1"/>
+    <col min="21" max="21" width="27.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4070,7 +2222,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -4101,16 +2253,8 @@
       <c r="T2" t="s">
         <v>28</v>
       </c>
-      <c r="V2" t="str">
-        <f>_xlfn.XLOOKUP(A2,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>产研办公室</v>
-      </c>
-      <c r="W2">
-        <f>_xlfn.XLOOKUP(A2,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="3" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -4154,7 +2298,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>40</v>
       </c>
@@ -4195,7 +2339,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>47</v>
       </c>
@@ -4236,7 +2380,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>52</v>
       </c>
@@ -4277,7 +2421,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>57</v>
       </c>
@@ -4315,7 +2459,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>62</v>
       </c>
@@ -4323,7 +2467,7 @@
         <v>63</v>
       </c>
       <c r="E8" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="F8" t="s">
         <v>54</v>
@@ -4352,16 +2496,8 @@
       <c r="S8" t="s">
         <v>68</v>
       </c>
-      <c r="V8" t="str">
-        <f>_xlfn.XLOOKUP(A8,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>外包</v>
-      </c>
-      <c r="W8" t="str">
-        <f>_xlfn.XLOOKUP(A8,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>外包</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="9" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>69</v>
       </c>
@@ -4402,7 +2538,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="10" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>72</v>
       </c>
@@ -4455,7 +2591,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="11" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>80</v>
       </c>
@@ -4495,16 +2631,8 @@
       <c r="S11" t="s">
         <v>86</v>
       </c>
-      <c r="V11" t="str">
-        <f>_xlfn.XLOOKUP(A11,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>研发治理部</v>
-      </c>
-      <c r="W11" t="str">
-        <f>_xlfn.XLOOKUP(A11,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>测试部</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="12" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>87</v>
       </c>
@@ -4545,7 +2673,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="13" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>92</v>
       </c>
@@ -4553,7 +2681,7 @@
         <v>23</v>
       </c>
       <c r="E13" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="F13" t="s">
         <v>73</v>
@@ -4573,16 +2701,8 @@
       <c r="T13" t="s">
         <v>94</v>
       </c>
-      <c r="V13" t="e">
-        <f>_xlfn.XLOOKUP(A13,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W13" t="e">
-        <f>_xlfn.XLOOKUP(A13,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="14" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>95</v>
       </c>
@@ -4590,7 +2710,7 @@
         <v>63</v>
       </c>
       <c r="E14" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="F14" t="s">
         <v>32</v>
@@ -4628,16 +2748,8 @@
       <c r="S14" t="s">
         <v>97</v>
       </c>
-      <c r="V14" t="str">
-        <f>_xlfn.XLOOKUP(A14,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>外包</v>
-      </c>
-      <c r="W14" t="str">
-        <f>_xlfn.XLOOKUP(A14,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>外包</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="15" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>98</v>
       </c>
@@ -4687,7 +2799,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="16" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>102</v>
       </c>
@@ -4712,16 +2824,8 @@
       <c r="U16" t="s">
         <v>105</v>
       </c>
-      <c r="V16" t="e">
-        <f>_xlfn.XLOOKUP(A16,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W16" t="e">
-        <f>_xlfn.XLOOKUP(A16,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="17" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>106</v>
       </c>
@@ -4774,7 +2878,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="18" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>112</v>
       </c>
@@ -4815,7 +2919,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="19" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>115</v>
       </c>
@@ -4856,7 +2960,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="20" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>117</v>
       </c>
@@ -4897,7 +3001,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="21" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>123</v>
       </c>
@@ -4905,7 +3009,7 @@
         <v>23</v>
       </c>
       <c r="E21" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="F21" t="s">
         <v>43</v>
@@ -4925,16 +3029,8 @@
       <c r="S21" t="s">
         <v>125</v>
       </c>
-      <c r="V21" t="e">
-        <f>_xlfn.XLOOKUP(A21,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W21" t="e">
-        <f>_xlfn.XLOOKUP(A21,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="22" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>126</v>
       </c>
@@ -4959,16 +3055,8 @@
       <c r="U22" t="s">
         <v>105</v>
       </c>
-      <c r="V22" t="e">
-        <f>_xlfn.XLOOKUP(A22,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W22" t="e">
-        <f>_xlfn.XLOOKUP(A22,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="23" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="23" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>128</v>
       </c>
@@ -5021,7 +3109,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="24" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>131</v>
       </c>
@@ -5029,10 +3117,10 @@
         <v>23</v>
       </c>
       <c r="E24" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="F24" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -5049,16 +3137,8 @@
       <c r="T24" t="s">
         <v>132</v>
       </c>
-      <c r="V24" t="str">
-        <f>_xlfn.XLOOKUP(A24,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>EKP18产品研发部</v>
-      </c>
-      <c r="W24">
-        <f>_xlfn.XLOOKUP(A24,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="25" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>133</v>
       </c>
@@ -5066,7 +3146,7 @@
         <v>63</v>
       </c>
       <c r="E25" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="F25" t="s">
         <v>54</v>
@@ -5095,16 +3175,8 @@
       <c r="S25" t="s">
         <v>135</v>
       </c>
-      <c r="V25" t="str">
-        <f>_xlfn.XLOOKUP(A25,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>外包</v>
-      </c>
-      <c r="W25" t="str">
-        <f>_xlfn.XLOOKUP(A25,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>外包</v>
-      </c>
-    </row>
-    <row r="26" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="26" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>136</v>
       </c>
@@ -5112,10 +3184,10 @@
         <v>23</v>
       </c>
       <c r="E26" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="F26" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="I26" t="s">
         <v>34</v>
@@ -5132,16 +3204,8 @@
       <c r="T26" t="s">
         <v>138</v>
       </c>
-      <c r="V26" t="str">
-        <f>_xlfn.XLOOKUP(A26,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>数据中台研发部</v>
-      </c>
-      <c r="W26">
-        <f>_xlfn.XLOOKUP(A26,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="27" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>139</v>
       </c>
@@ -5181,16 +3245,8 @@
       <c r="S27" t="s">
         <v>141</v>
       </c>
-      <c r="V27" t="str">
-        <f>_xlfn.XLOOKUP(A27,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>研发治理部</v>
-      </c>
-      <c r="W27" t="str">
-        <f>_xlfn.XLOOKUP(A27,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>测试部</v>
-      </c>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.15">
+    </row>
+    <row r="28" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>142</v>
       </c>
@@ -5221,16 +3277,8 @@
       <c r="S28" t="s">
         <v>144</v>
       </c>
-      <c r="V28" t="str">
-        <f>_xlfn.XLOOKUP(A28,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>产研办公室</v>
-      </c>
-      <c r="W28">
-        <f>_xlfn.XLOOKUP(A28,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="29" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>145</v>
       </c>
@@ -5270,16 +3318,8 @@
       <c r="S29" t="s">
         <v>146</v>
       </c>
-      <c r="V29" t="str">
-        <f>_xlfn.XLOOKUP(A29,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>研发治理部</v>
-      </c>
-      <c r="W29" t="str">
-        <f>_xlfn.XLOOKUP(A29,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>测试部</v>
-      </c>
-    </row>
-    <row r="30" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="30" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>147</v>
       </c>
@@ -5319,16 +3359,8 @@
       <c r="S30" t="s">
         <v>122</v>
       </c>
-      <c r="V30" t="str">
-        <f>_xlfn.XLOOKUP(A30,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>研发治理部</v>
-      </c>
-      <c r="W30" t="str">
-        <f>_xlfn.XLOOKUP(A30,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>测试部</v>
-      </c>
-    </row>
-    <row r="31" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="31" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>148</v>
       </c>
@@ -5369,7 +3401,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="32" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>150</v>
       </c>
@@ -5394,16 +3426,8 @@
       <c r="U32" t="s">
         <v>105</v>
       </c>
-      <c r="V32" t="e">
-        <f>_xlfn.XLOOKUP(A32,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W32" t="e">
-        <f>_xlfn.XLOOKUP(A32,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="33" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="33" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>152</v>
       </c>
@@ -5441,7 +3465,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="34" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>156</v>
       </c>
@@ -5479,7 +3503,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>158</v>
       </c>
@@ -5517,7 +3541,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="36" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>162</v>
       </c>
@@ -5555,7 +3579,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="37" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>165</v>
       </c>
@@ -5592,16 +3616,8 @@
       <c r="S37" t="s">
         <v>167</v>
       </c>
-      <c r="V37" t="str">
-        <f>_xlfn.XLOOKUP(A37,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>研发治理部</v>
-      </c>
-      <c r="W37" t="str">
-        <f>_xlfn.XLOOKUP(A37,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>效能提升组</v>
-      </c>
-    </row>
-    <row r="38" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="38" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>168</v>
       </c>
@@ -5638,16 +3654,8 @@
       <c r="S38" t="s">
         <v>170</v>
       </c>
-      <c r="V38" t="str">
-        <f>_xlfn.XLOOKUP(A38,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>研发治理部</v>
-      </c>
-      <c r="W38" t="str">
-        <f>_xlfn.XLOOKUP(A38,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>配置管理组</v>
-      </c>
-    </row>
-    <row r="39" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="39" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>171</v>
       </c>
@@ -5688,7 +3696,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="40" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>175</v>
       </c>
@@ -5726,7 +3734,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="41" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>179</v>
       </c>
@@ -5764,7 +3772,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>183</v>
       </c>
@@ -5805,7 +3813,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="43" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>186</v>
       </c>
@@ -5843,7 +3851,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>189</v>
       </c>
@@ -5884,7 +3892,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="45" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>191</v>
       </c>
@@ -5922,7 +3930,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="46" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>193</v>
       </c>
@@ -5963,7 +3971,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="47" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>196</v>
       </c>
@@ -6001,7 +4009,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="48" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>198</v>
       </c>
@@ -6044,16 +4052,8 @@
       <c r="S48" t="s">
         <v>201</v>
       </c>
-      <c r="V48" t="str">
-        <f>_xlfn.XLOOKUP(A48,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>研发治理部</v>
-      </c>
-      <c r="W48" t="str">
-        <f>_xlfn.XLOOKUP(A48,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>测试部</v>
-      </c>
-    </row>
-    <row r="49" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="49" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>202</v>
       </c>
@@ -6090,16 +4090,8 @@
       <c r="S49" t="s">
         <v>204</v>
       </c>
-      <c r="V49" t="str">
-        <f>_xlfn.XLOOKUP(A49,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>研发治理部</v>
-      </c>
-      <c r="W49" t="str">
-        <f>_xlfn.XLOOKUP(A49,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>配置管理组</v>
-      </c>
-    </row>
-    <row r="50" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="50" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>205</v>
       </c>
@@ -6137,7 +4129,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="51" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>207</v>
       </c>
@@ -6178,7 +4170,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="52" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>209</v>
       </c>
@@ -6200,16 +4192,8 @@
       <c r="S52" t="s">
         <v>210</v>
       </c>
-      <c r="V52" t="str">
-        <f>_xlfn.XLOOKUP(A52,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>产品研发中心</v>
-      </c>
-      <c r="W52">
-        <f>_xlfn.XLOOKUP(A52,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="53" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>211</v>
       </c>
@@ -6249,16 +4233,8 @@
       <c r="S53" t="s">
         <v>213</v>
       </c>
-      <c r="V53" t="str">
-        <f>_xlfn.XLOOKUP(A53,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>研发治理部</v>
-      </c>
-      <c r="W53" t="str">
-        <f>_xlfn.XLOOKUP(A53,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>测试部</v>
-      </c>
-    </row>
-    <row r="54" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="54" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>214</v>
       </c>
@@ -6296,7 +4272,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="55" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>217</v>
       </c>
@@ -6334,7 +4310,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="56" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>220</v>
       </c>
@@ -6384,7 +4360,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="57" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>222</v>
       </c>
@@ -6424,16 +4400,8 @@
       <c r="S57" t="s">
         <v>223</v>
       </c>
-      <c r="V57" t="str">
-        <f>_xlfn.XLOOKUP(A57,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>研发治理部</v>
-      </c>
-      <c r="W57" t="str">
-        <f>_xlfn.XLOOKUP(A57,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>测试部</v>
-      </c>
-    </row>
-    <row r="58" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="58" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>224</v>
       </c>
@@ -6474,7 +4442,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="59" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>226</v>
       </c>
@@ -6524,7 +4492,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="60" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>228</v>
       </c>
@@ -6574,7 +4542,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>230</v>
       </c>
@@ -6605,16 +4573,8 @@
       <c r="S61" t="s">
         <v>232</v>
       </c>
-      <c r="V61" t="str">
-        <f>_xlfn.XLOOKUP(A61,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>产研办公室</v>
-      </c>
-      <c r="W61">
-        <f>_xlfn.XLOOKUP(A61,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="62" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>233</v>
       </c>
@@ -6655,7 +4615,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="63" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>235</v>
       </c>
@@ -6696,7 +4656,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="64" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>238</v>
       </c>
@@ -6736,16 +4696,8 @@
       <c r="S64" t="s">
         <v>240</v>
       </c>
-      <c r="V64" t="str">
-        <f>_xlfn.XLOOKUP(A64,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>研发治理部</v>
-      </c>
-      <c r="W64" t="str">
-        <f>_xlfn.XLOOKUP(A64,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>测试部</v>
-      </c>
-    </row>
-    <row r="65" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="65" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>241</v>
       </c>
@@ -6786,7 +4738,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="66" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>243</v>
       </c>
@@ -6827,7 +4779,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="67" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>245</v>
       </c>
@@ -6868,7 +4820,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="68" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>247</v>
       </c>
@@ -6896,16 +4848,8 @@
       <c r="T68" t="s">
         <v>250</v>
       </c>
-      <c r="V68" t="str">
-        <f>_xlfn.XLOOKUP(A68,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>用户运营组</v>
-      </c>
-      <c r="W68">
-        <f>_xlfn.XLOOKUP(A68,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="69" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>251</v>
       </c>
@@ -6913,7 +4857,7 @@
         <v>63</v>
       </c>
       <c r="E69" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="F69" t="s">
         <v>48</v>
@@ -6942,16 +4886,8 @@
       <c r="S69" s="4">
         <v>45658</v>
       </c>
-      <c r="V69" t="str">
-        <f>_xlfn.XLOOKUP(A69,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>外包</v>
-      </c>
-      <c r="W69" t="str">
-        <f>_xlfn.XLOOKUP(A69,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>外包</v>
-      </c>
-    </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.15">
+    </row>
+    <row r="70" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>253</v>
       </c>
@@ -6989,7 +4925,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="71" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>258</v>
       </c>
@@ -7027,7 +4963,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>260</v>
       </c>
@@ -7058,16 +4994,8 @@
       <c r="S72" t="s">
         <v>261</v>
       </c>
-      <c r="V72" t="str">
-        <f>_xlfn.XLOOKUP(A72,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>产研办公室</v>
-      </c>
-      <c r="W72">
-        <f>_xlfn.XLOOKUP(A72,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="73" spans="1:21" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>262</v>
       </c>
@@ -7105,7 +5033,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="74" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>267</v>
       </c>
@@ -7146,7 +5074,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="75" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>268</v>
       </c>
@@ -7171,16 +5099,8 @@
       <c r="U75" t="s">
         <v>105</v>
       </c>
-      <c r="V75" t="e">
-        <f>_xlfn.XLOOKUP(A75,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W75" t="e">
-        <f>_xlfn.XLOOKUP(A75,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.15">
+    </row>
+    <row r="76" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>270</v>
       </c>
@@ -7221,7 +5141,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="77" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>272</v>
       </c>
@@ -7261,16 +5181,8 @@
       <c r="S77" t="s">
         <v>273</v>
       </c>
-      <c r="V77" t="str">
-        <f>_xlfn.XLOOKUP(A77,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>研发治理部</v>
-      </c>
-      <c r="W77" t="str">
-        <f>_xlfn.XLOOKUP(A77,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>测试部</v>
-      </c>
-    </row>
-    <row r="78" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="78" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>274</v>
       </c>
@@ -7320,7 +5232,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="79" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>276</v>
       </c>
@@ -7358,7 +5270,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="80" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>277</v>
       </c>
@@ -7396,7 +5308,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="81" spans="1:23" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:21" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>279</v>
       </c>
@@ -7407,13 +5319,13 @@
         <v>63</v>
       </c>
       <c r="E81" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="F81" t="s">
         <v>118</v>
       </c>
       <c r="H81" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="I81" t="s">
         <v>120</v>
@@ -7436,16 +5348,8 @@
       <c r="T81" t="s">
         <v>94</v>
       </c>
-      <c r="V81" t="str">
-        <f>_xlfn.XLOOKUP(A81,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>KK组</v>
-      </c>
-      <c r="W81">
-        <f>_xlfn.XLOOKUP(A81,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:23" x14ac:dyDescent="0.15">
+    </row>
+    <row r="82" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>282</v>
       </c>
@@ -7464,9 +5368,6 @@
       <c r="I82" t="s">
         <v>25</v>
       </c>
-      <c r="O82" t="s">
-        <v>284</v>
-      </c>
       <c r="Q82" t="s">
         <v>26</v>
       </c>
@@ -7482,16 +5383,8 @@
       <c r="U82" t="s">
         <v>105</v>
       </c>
-      <c r="V82" t="str">
-        <f>_xlfn.XLOOKUP(A82,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>产研办公室</v>
-      </c>
-      <c r="W82">
-        <f>_xlfn.XLOOKUP(A82,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="83" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>286</v>
       </c>
@@ -7535,7 +5428,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="84" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>287</v>
       </c>
@@ -7576,7 +5469,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="85" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>290</v>
       </c>
@@ -7617,7 +5510,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="86" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>293</v>
       </c>
@@ -7655,7 +5548,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="87" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>296</v>
       </c>
@@ -7693,7 +5586,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="88" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>299</v>
       </c>
@@ -7733,16 +5626,8 @@
       <c r="S88" t="s">
         <v>300</v>
       </c>
-      <c r="V88" t="str">
-        <f>_xlfn.XLOOKUP(A88,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>研发治理部</v>
-      </c>
-      <c r="W88" t="str">
-        <f>_xlfn.XLOOKUP(A88,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>测试部</v>
-      </c>
-    </row>
-    <row r="89" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>301</v>
       </c>
@@ -7786,7 +5671,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="90" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>305</v>
       </c>
@@ -7814,16 +5699,8 @@
       <c r="S90" t="s">
         <v>125</v>
       </c>
-      <c r="V90" t="e">
-        <f>_xlfn.XLOOKUP(A90,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W90" t="e">
-        <f>_xlfn.XLOOKUP(A90,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="91" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="91" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>306</v>
       </c>
@@ -7864,7 +5741,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="92" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>308</v>
       </c>
@@ -7889,16 +5766,8 @@
       <c r="U92" t="s">
         <v>105</v>
       </c>
-      <c r="V92" t="e">
-        <f>_xlfn.XLOOKUP(A92,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W92" t="e">
-        <f>_xlfn.XLOOKUP(A92,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="93" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="93" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>310</v>
       </c>
@@ -7932,16 +5801,8 @@
       <c r="S93" t="s">
         <v>97</v>
       </c>
-      <c r="V93" t="str">
-        <f>_xlfn.XLOOKUP(A93,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>华南开发一组</v>
-      </c>
-      <c r="W93">
-        <f>_xlfn.XLOOKUP(A93,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="94" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>311</v>
       </c>
@@ -7955,7 +5816,7 @@
         <v>177</v>
       </c>
       <c r="I94" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="Q94" t="s">
         <v>26</v>
@@ -7969,16 +5830,8 @@
       <c r="T94" t="s">
         <v>314</v>
       </c>
-      <c r="V94" t="str">
-        <f>_xlfn.XLOOKUP(A94,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>智能中台体验组</v>
-      </c>
-      <c r="W94">
-        <f>_xlfn.XLOOKUP(A94,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="95" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>315</v>
       </c>
@@ -8015,16 +5868,8 @@
       <c r="S95" t="s">
         <v>318</v>
       </c>
-      <c r="V95" t="str">
-        <f>_xlfn.XLOOKUP(A95,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>研发治理部</v>
-      </c>
-      <c r="W95" t="str">
-        <f>_xlfn.XLOOKUP(A95,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>三快支持组</v>
-      </c>
-    </row>
-    <row r="96" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="96" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>319</v>
       </c>
@@ -8052,16 +5897,8 @@
       <c r="T96" t="s">
         <v>321</v>
       </c>
-      <c r="V96" t="e">
-        <f>_xlfn.XLOOKUP(A96,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W96" t="e">
-        <f>_xlfn.XLOOKUP(A96,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="97" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="97" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>322</v>
       </c>
@@ -8102,7 +5939,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="98" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>324</v>
       </c>
@@ -8143,7 +5980,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="99" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>326</v>
       </c>
@@ -8183,16 +6020,8 @@
       <c r="S99" t="s">
         <v>327</v>
       </c>
-      <c r="V99" t="str">
-        <f>_xlfn.XLOOKUP(A99,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>研发治理部</v>
-      </c>
-      <c r="W99" t="str">
-        <f>_xlfn.XLOOKUP(A99,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>测试部</v>
-      </c>
-    </row>
-    <row r="100" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="100" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>328</v>
       </c>
@@ -8242,7 +6071,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="101" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>330</v>
       </c>
@@ -8283,7 +6112,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="102" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>332</v>
       </c>
@@ -8333,7 +6162,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="103" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>334</v>
       </c>
@@ -8341,10 +6170,10 @@
         <v>23</v>
       </c>
       <c r="E103" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="F103" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="I103" t="s">
         <v>85</v>
@@ -8361,16 +6190,8 @@
       <c r="T103" t="s">
         <v>321</v>
       </c>
-      <c r="V103" t="str">
-        <f>_xlfn.XLOOKUP(A103,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>智能中台测试组</v>
-      </c>
-      <c r="W103">
-        <f>_xlfn.XLOOKUP(A103,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="104" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>336</v>
       </c>
@@ -8378,10 +6199,10 @@
         <v>23</v>
       </c>
       <c r="E104" t="s">
+        <v>523</v>
+      </c>
+      <c r="F104" t="s">
         <v>527</v>
-      </c>
-      <c r="F104" t="s">
-        <v>531</v>
       </c>
       <c r="I104" t="s">
         <v>34</v>
@@ -8398,16 +6219,8 @@
       <c r="T104" t="s">
         <v>338</v>
       </c>
-      <c r="V104" t="e">
-        <f>_xlfn.XLOOKUP(A104,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W104" t="e">
-        <f>_xlfn.XLOOKUP(A104,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="105" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="105" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>339</v>
       </c>
@@ -8445,7 +6258,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="106" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>341</v>
       </c>
@@ -8486,7 +6299,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="107" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>344</v>
       </c>
@@ -8524,7 +6337,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="108" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>346</v>
       </c>
@@ -8565,7 +6378,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="109" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>348</v>
       </c>
@@ -8603,7 +6416,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="110" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>349</v>
       </c>
@@ -8653,7 +6466,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="111" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>351</v>
       </c>
@@ -8691,7 +6504,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="112" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>353</v>
       </c>
@@ -8729,7 +6542,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="113" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>356</v>
       </c>
@@ -8779,7 +6592,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="114" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>359</v>
       </c>
@@ -8829,7 +6642,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="115" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>361</v>
       </c>
@@ -8870,7 +6683,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="116" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>363</v>
       </c>
@@ -8898,16 +6711,8 @@
       <c r="U116" t="s">
         <v>105</v>
       </c>
-      <c r="V116" t="e">
-        <f>_xlfn.XLOOKUP(A116,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W116" t="e">
-        <f>_xlfn.XLOOKUP(A116,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="117" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="117" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>365</v>
       </c>
@@ -8947,16 +6752,8 @@
       <c r="S117" t="s">
         <v>368</v>
       </c>
-      <c r="V117" t="str">
-        <f>_xlfn.XLOOKUP(A117,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>研发治理部</v>
-      </c>
-      <c r="W117" t="str">
-        <f>_xlfn.XLOOKUP(A117,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>效能提升组</v>
-      </c>
-    </row>
-    <row r="118" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="118" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>369</v>
       </c>
@@ -8966,9 +6763,6 @@
       <c r="I118" t="s">
         <v>103</v>
       </c>
-      <c r="O118" t="s">
-        <v>370</v>
-      </c>
       <c r="Q118" t="s">
         <v>26</v>
       </c>
@@ -8976,23 +6770,18 @@
         <v>103</v>
       </c>
       <c r="S118" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="T118" t="s">
         <v>138</v>
       </c>
-      <c r="V118" t="e">
-        <f>_xlfn.XLOOKUP(A118,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W118" t="e">
-        <f>_xlfn.XLOOKUP(A118,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="119" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+      <c r="U118" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="119" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B119">
         <v>11201005</v>
@@ -9037,21 +6826,21 @@
         <v>34</v>
       </c>
       <c r="S119" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="120" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="120" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
-      <c r="A120" t="s">
-        <v>374</v>
-      </c>
       <c r="D120" t="s">
         <v>23</v>
       </c>
       <c r="E120" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="F120" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="I120" t="s">
         <v>85</v>
@@ -9063,23 +6852,15 @@
         <v>85</v>
       </c>
       <c r="S120" t="s">
+        <v>374</v>
+      </c>
+      <c r="T120" t="s">
         <v>375</v>
       </c>
-      <c r="T120" t="s">
+    </row>
+    <row r="121" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
         <v>376</v>
-      </c>
-      <c r="V120" t="e">
-        <f>_xlfn.XLOOKUP(A120,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W120" t="e">
-        <f>_xlfn.XLOOKUP(A120,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="121" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
-      <c r="A121" t="s">
-        <v>377</v>
       </c>
       <c r="B121">
         <v>12203722</v>
@@ -9124,18 +6905,18 @@
         <v>49</v>
       </c>
       <c r="S121" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="122" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
         <v>378</v>
-      </c>
-    </row>
-    <row r="122" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
-      <c r="A122" t="s">
-        <v>379</v>
       </c>
       <c r="B122">
         <v>12420802</v>
       </c>
       <c r="C122" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D122" t="s">
         <v>23</v>
@@ -9162,12 +6943,12 @@
         <v>34</v>
       </c>
       <c r="S122" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="123" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
         <v>381</v>
-      </c>
-    </row>
-    <row r="123" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
-      <c r="A123" t="s">
-        <v>382</v>
       </c>
       <c r="B123">
         <v>11700937</v>
@@ -9200,24 +6981,24 @@
         <v>34</v>
       </c>
       <c r="S123" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="124" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
         <v>383</v>
-      </c>
-    </row>
-    <row r="124" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
-      <c r="A124" t="s">
-        <v>384</v>
       </c>
       <c r="D124" t="s">
         <v>63</v>
       </c>
       <c r="E124" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="F124" t="s">
         <v>48</v>
       </c>
       <c r="H124" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="I124" t="s">
         <v>49</v>
@@ -9226,7 +7007,7 @@
         <v>50</v>
       </c>
       <c r="O124" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="P124" t="s">
         <v>67</v>
@@ -9240,24 +7021,16 @@
       <c r="S124" t="s">
         <v>97</v>
       </c>
-      <c r="V124" t="str">
-        <f>_xlfn.XLOOKUP(A124,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>外包</v>
-      </c>
-      <c r="W124" t="str">
-        <f>_xlfn.XLOOKUP(A124,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>外包</v>
-      </c>
-    </row>
-    <row r="125" spans="1:23" x14ac:dyDescent="0.15">
+    </row>
+    <row r="125" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D125" t="s">
         <v>23</v>
       </c>
       <c r="E125" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="I125" t="s">
         <v>25</v>
@@ -9269,7 +7042,7 @@
         <v>25</v>
       </c>
       <c r="S125" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="T125" t="s">
         <v>285</v>
@@ -9277,18 +7050,10 @@
       <c r="U125" t="s">
         <v>105</v>
       </c>
-      <c r="V125" t="e">
-        <f>_xlfn.XLOOKUP(A125,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W125" t="e">
-        <f>_xlfn.XLOOKUP(A125,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="126" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="126" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B126">
         <v>11401341</v>
@@ -9324,12 +7089,12 @@
         <v>34</v>
       </c>
       <c r="S126" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="127" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
         <v>389</v>
-      </c>
-    </row>
-    <row r="127" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
-      <c r="A127" t="s">
-        <v>390</v>
       </c>
       <c r="B127">
         <v>12203884</v>
@@ -9365,15 +7130,15 @@
         <v>34</v>
       </c>
       <c r="S127" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="U127" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="128" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B128">
         <v>11902241</v>
@@ -9406,12 +7171,12 @@
         <v>178</v>
       </c>
       <c r="S128" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="129" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
         <v>393</v>
-      </c>
-    </row>
-    <row r="129" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A129" t="s">
-        <v>394</v>
       </c>
       <c r="B129">
         <v>22620710</v>
@@ -9446,18 +7211,10 @@
       <c r="U129" t="s">
         <v>105</v>
       </c>
-      <c r="V129" t="str">
-        <f>_xlfn.XLOOKUP(A129,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>产研办公室</v>
-      </c>
-      <c r="W129">
-        <f>_xlfn.XLOOKUP(A129,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="130" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B130">
         <v>12103017</v>
@@ -9493,26 +7250,18 @@
         <v>85</v>
       </c>
       <c r="S130" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="131" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
         <v>396</v>
-      </c>
-      <c r="V130" t="str">
-        <f>_xlfn.XLOOKUP(A130,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>研发治理部</v>
-      </c>
-      <c r="W130" t="str">
-        <f>_xlfn.XLOOKUP(A130,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>测试部</v>
-      </c>
-    </row>
-    <row r="131" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
-      <c r="A131" t="s">
-        <v>397</v>
       </c>
       <c r="D131" t="s">
         <v>63</v>
       </c>
       <c r="E131" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="F131" t="s">
         <v>54</v>
@@ -9527,7 +7276,7 @@
         <v>65</v>
       </c>
       <c r="O131" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="P131" t="s">
         <v>67</v>
@@ -9541,18 +7290,10 @@
       <c r="S131" s="2">
         <v>45764</v>
       </c>
-      <c r="V131" t="str">
-        <f>_xlfn.XLOOKUP(A131,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>外包</v>
-      </c>
-      <c r="W131" t="str">
-        <f>_xlfn.XLOOKUP(A131,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>外包</v>
-      </c>
-    </row>
-    <row r="132" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="132" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B132">
         <v>12520899</v>
@@ -9585,18 +7326,18 @@
         <v>60</v>
       </c>
       <c r="S132" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="133" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="133" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
-      <c r="A133" t="s">
-        <v>401</v>
-      </c>
       <c r="D133" t="s">
         <v>23</v>
       </c>
       <c r="E133" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="F133" t="s">
         <v>59</v>
@@ -9605,7 +7346,7 @@
         <v>60</v>
       </c>
       <c r="P133" t="s">
-        <v>402</v>
+        <v>37</v>
       </c>
       <c r="Q133" t="s">
         <v>124</v>
@@ -9614,26 +7355,18 @@
         <v>60</v>
       </c>
       <c r="S133" t="s">
-        <v>403</v>
-      </c>
-      <c r="V133" t="e">
-        <f>_xlfn.XLOOKUP(A133,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W133" t="e">
-        <f>_xlfn.XLOOKUP(A133,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="134" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="134" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B134">
         <v>11301244</v>
       </c>
       <c r="C134" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D134" t="s">
         <v>23</v>
@@ -9660,18 +7393,18 @@
         <v>25</v>
       </c>
       <c r="S134" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="135" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="135" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D135" t="s">
         <v>63</v>
       </c>
       <c r="E135" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="F135" t="s">
         <v>54</v>
@@ -9686,7 +7419,7 @@
         <v>65</v>
       </c>
       <c r="O135" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="P135" t="s">
         <v>67</v>
@@ -9700,24 +7433,16 @@
       <c r="S135" s="4">
         <v>45820</v>
       </c>
-      <c r="V135" t="str">
-        <f>_xlfn.XLOOKUP(A135,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>外包</v>
-      </c>
-      <c r="W135" t="str">
-        <f>_xlfn.XLOOKUP(A135,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>外包</v>
-      </c>
-    </row>
-    <row r="136" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="136" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B136">
         <v>12213814</v>
       </c>
       <c r="C136" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D136" t="s">
         <v>23</v>
@@ -9762,9 +7487,9 @@
         <v>327</v>
       </c>
     </row>
-    <row r="137" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B137">
         <v>12003735</v>
@@ -9797,26 +7522,18 @@
         <v>34</v>
       </c>
       <c r="S137" t="s">
-        <v>412</v>
-      </c>
-      <c r="V137" t="str">
-        <f>_xlfn.XLOOKUP(A137,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>研发治理部</v>
-      </c>
-      <c r="W137" t="str">
-        <f>_xlfn.XLOOKUP(A137,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>配置管理组</v>
-      </c>
-    </row>
-    <row r="138" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="138" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B138">
         <v>10600090</v>
       </c>
       <c r="C138" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D138" t="s">
         <v>23</v>
@@ -9843,20 +7560,12 @@
         <v>25</v>
       </c>
       <c r="S138" t="s">
-        <v>415</v>
-      </c>
-      <c r="V138" t="str">
-        <f>_xlfn.XLOOKUP(A138,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>研发治理部</v>
-      </c>
-      <c r="W138" t="str">
-        <f>_xlfn.XLOOKUP(A138,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>配置管理组</v>
-      </c>
-    </row>
-    <row r="139" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="139" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B139">
         <v>12320322</v>
@@ -9892,9 +7601,9 @@
         <v>292</v>
       </c>
     </row>
-    <row r="140" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B140">
         <v>11800335</v>
@@ -9939,12 +7648,12 @@
         <v>34</v>
       </c>
       <c r="S140" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="141" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="141" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B141">
         <v>11901268</v>
@@ -9980,12 +7689,12 @@
         <v>34</v>
       </c>
       <c r="S141" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="142" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="142" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B142">
         <v>11700733</v>
@@ -10021,20 +7730,12 @@
         <v>85</v>
       </c>
       <c r="S142" t="s">
-        <v>422</v>
-      </c>
-      <c r="V142" t="str">
-        <f>_xlfn.XLOOKUP(A142,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>研发治理部</v>
-      </c>
-      <c r="W142" t="str">
-        <f>_xlfn.XLOOKUP(A142,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>测试部</v>
-      </c>
-    </row>
-    <row r="143" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="143" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D143" t="s">
         <v>23</v>
@@ -10046,30 +7747,30 @@
         <v>129</v>
       </c>
       <c r="H143" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="I143" t="s">
         <v>49</v>
       </c>
       <c r="O143" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="Q143" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="R143" t="s">
         <v>49</v>
       </c>
       <c r="S143" t="s">
+        <v>425</v>
+      </c>
+      <c r="T143" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="144" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
         <v>427</v>
-      </c>
-      <c r="T143" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="144" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A144" t="s">
-        <v>429</v>
       </c>
       <c r="D144" t="s">
         <v>23</v>
@@ -10087,23 +7788,15 @@
         <v>25</v>
       </c>
       <c r="S144" t="s">
+        <v>428</v>
+      </c>
+      <c r="T144" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="145" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
         <v>430</v>
-      </c>
-      <c r="T144" t="s">
-        <v>431</v>
-      </c>
-      <c r="V144" t="str">
-        <f>_xlfn.XLOOKUP(A144,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>产研办公室</v>
-      </c>
-      <c r="W144">
-        <f>_xlfn.XLOOKUP(A144,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
-      <c r="A145" t="s">
-        <v>432</v>
       </c>
       <c r="B145">
         <v>11301219</v>
@@ -10148,12 +7841,12 @@
         <v>34</v>
       </c>
       <c r="S145" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="146" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="146" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B146">
         <v>11301177</v>
@@ -10189,12 +7882,12 @@
         <v>120</v>
       </c>
       <c r="S146" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="147" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="147" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B147">
         <v>11901227</v>
@@ -10230,24 +7923,24 @@
         <v>34</v>
       </c>
       <c r="S147" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="148" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="148" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D148" t="s">
         <v>63</v>
       </c>
       <c r="E148" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="F148" t="s">
         <v>43</v>
       </c>
       <c r="H148" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="I148" t="s">
         <v>34</v>
@@ -10270,18 +7963,10 @@
       <c r="S148" s="4">
         <v>45946</v>
       </c>
-      <c r="V148" t="str">
-        <f>_xlfn.XLOOKUP(A148,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>外包</v>
-      </c>
-      <c r="W148" t="str">
-        <f>_xlfn.XLOOKUP(A148,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>外包</v>
-      </c>
-    </row>
-    <row r="149" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="149" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B149">
         <v>11401522</v>
@@ -10314,12 +7999,12 @@
         <v>60</v>
       </c>
       <c r="S149" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="150" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="150" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B150">
         <v>12003770</v>
@@ -10355,9 +8040,9 @@
         <v>259</v>
       </c>
     </row>
-    <row r="151" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B151">
         <v>12102509</v>
@@ -10390,18 +8075,18 @@
         <v>60</v>
       </c>
       <c r="S151" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="152" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="152" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B152">
         <v>11801162</v>
       </c>
       <c r="C152" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D152" t="s">
         <v>23</v>
@@ -10428,18 +8113,18 @@
         <v>60</v>
       </c>
       <c r="S152" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="153" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="153" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D153" t="s">
         <v>23</v>
       </c>
       <c r="E153" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="F153" t="s">
         <v>43</v>
@@ -10451,15 +8136,15 @@
         <v>26</v>
       </c>
       <c r="S153" t="s">
+        <v>446</v>
+      </c>
+      <c r="T153" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="154" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
         <v>448</v>
-      </c>
-      <c r="T153" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="154" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
-      <c r="A154" t="s">
-        <v>450</v>
       </c>
       <c r="B154">
         <v>11902300</v>
@@ -10495,20 +8180,12 @@
         <v>34</v>
       </c>
       <c r="S154" t="s">
-        <v>451</v>
-      </c>
-      <c r="V154" t="str">
-        <f>_xlfn.XLOOKUP(A154,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>研发治理部</v>
-      </c>
-      <c r="W154" t="str">
-        <f>_xlfn.XLOOKUP(A154,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>效能提升组</v>
-      </c>
-    </row>
-    <row r="155" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="155" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B155">
         <v>11902153</v>
@@ -10547,21 +8224,21 @@
         <v>116</v>
       </c>
     </row>
-    <row r="156" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D156" t="s">
         <v>23</v>
       </c>
       <c r="E156" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="I156" t="s">
         <v>34</v>
       </c>
       <c r="O156" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="Q156" t="s">
         <v>26</v>
@@ -10570,29 +8247,21 @@
         <v>34</v>
       </c>
       <c r="S156" t="s">
+        <v>453</v>
+      </c>
+      <c r="T156" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="157" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
         <v>455</v>
-      </c>
-      <c r="T156" t="s">
-        <v>456</v>
-      </c>
-      <c r="V156" t="str">
-        <f>_xlfn.XLOOKUP(A156,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>EKP18产品研发部</v>
-      </c>
-      <c r="W156">
-        <f>_xlfn.XLOOKUP(A156,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
-      <c r="A157" t="s">
-        <v>457</v>
       </c>
       <c r="B157">
         <v>11401527</v>
       </c>
       <c r="C157" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="D157" t="s">
         <v>23</v>
@@ -10619,12 +8288,12 @@
         <v>60</v>
       </c>
       <c r="S157" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="158" spans="1:23" x14ac:dyDescent="0.15">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="158" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B158">
         <v>12002555</v>
@@ -10654,12 +8323,12 @@
         <v>25</v>
       </c>
       <c r="S158" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="159" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="159" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B159">
         <v>11901982</v>
@@ -10695,12 +8364,12 @@
         <v>34</v>
       </c>
       <c r="S159" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="160" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="160" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B160">
         <v>12002553</v>
@@ -10736,18 +8405,18 @@
         <v>34</v>
       </c>
       <c r="S160" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="161" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="161" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D161" t="s">
         <v>63</v>
       </c>
       <c r="E161" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="F161" t="s">
         <v>83</v>
@@ -10759,7 +8428,7 @@
         <v>85</v>
       </c>
       <c r="O161" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="P161" t="s">
         <v>67</v>
@@ -10771,20 +8440,12 @@
         <v>85</v>
       </c>
       <c r="S161" t="s">
-        <v>467</v>
-      </c>
-      <c r="V161" t="str">
-        <f>_xlfn.XLOOKUP(A161,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>外包</v>
-      </c>
-      <c r="W161" t="str">
-        <f>_xlfn.XLOOKUP(A161,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>外包</v>
-      </c>
-    </row>
-    <row r="162" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="162" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B162">
         <v>12003972</v>
@@ -10796,10 +8457,10 @@
         <v>23</v>
       </c>
       <c r="E162" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="F162" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="G162" t="s">
         <v>84</v>
@@ -10820,20 +8481,12 @@
         <v>85</v>
       </c>
       <c r="S162" t="s">
-        <v>469</v>
-      </c>
-      <c r="V162" t="str">
-        <f>_xlfn.XLOOKUP(A162,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>研发治理部</v>
-      </c>
-      <c r="W162" t="str">
-        <f>_xlfn.XLOOKUP(A162,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>测试部</v>
-      </c>
-    </row>
-    <row r="163" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="163" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B163">
         <v>12003947</v>
@@ -10878,18 +8531,18 @@
         <v>49</v>
       </c>
       <c r="S163" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="164" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="164" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D164" t="s">
         <v>63</v>
       </c>
       <c r="E164" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="F164" t="s">
         <v>54</v>
@@ -10904,7 +8557,7 @@
         <v>65</v>
       </c>
       <c r="O164" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="P164" t="s">
         <v>67</v>
@@ -10916,20 +8569,12 @@
         <v>34</v>
       </c>
       <c r="S164" t="s">
-        <v>474</v>
-      </c>
-      <c r="V164" t="e">
-        <f>_xlfn.XLOOKUP(A164,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W164" t="e">
-        <f>_xlfn.XLOOKUP(A164,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="165" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="165" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B165">
         <v>22620691</v>
@@ -10965,35 +8610,27 @@
         <v>85</v>
       </c>
       <c r="S165" t="s">
-        <v>476</v>
-      </c>
-      <c r="V165" t="str">
-        <f>_xlfn.XLOOKUP(A165,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>研发治理部</v>
-      </c>
-      <c r="W165" t="str">
-        <f>_xlfn.XLOOKUP(A165,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>测试部</v>
-      </c>
-    </row>
-    <row r="166" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="166" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D166" t="s">
         <v>23</v>
       </c>
       <c r="E166" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="F166" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="I166" t="s">
         <v>60</v>
       </c>
       <c r="O166" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="Q166" t="s">
         <v>26</v>
@@ -11007,18 +8644,10 @@
       <c r="T166" t="s">
         <v>138</v>
       </c>
-      <c r="V166" t="str">
-        <f>_xlfn.XLOOKUP(A166,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>智能中台规划部</v>
-      </c>
-      <c r="W166">
-        <f>_xlfn.XLOOKUP(A166,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="167" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B167">
         <v>11301232</v>
@@ -11057,18 +8686,18 @@
         <v>164</v>
       </c>
     </row>
-    <row r="168" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D168" t="s">
         <v>23</v>
       </c>
       <c r="E168" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="F168" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="I168" t="s">
         <v>34</v>
@@ -11080,23 +8709,15 @@
         <v>34</v>
       </c>
       <c r="S168" t="s">
+        <v>478</v>
+      </c>
+      <c r="T168" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="169" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
         <v>480</v>
-      </c>
-      <c r="T168" t="s">
-        <v>481</v>
-      </c>
-      <c r="V168" t="str">
-        <f>_xlfn.XLOOKUP(A168,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>治理&amp;算法组</v>
-      </c>
-      <c r="W168">
-        <f>_xlfn.XLOOKUP(A168,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
-      <c r="A169" t="s">
-        <v>482</v>
       </c>
       <c r="B169">
         <v>11901945</v>
@@ -11129,12 +8750,12 @@
         <v>34</v>
       </c>
       <c r="S169" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="170" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="170" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B170">
         <v>12103439</v>
@@ -11179,12 +8800,12 @@
         <v>49</v>
       </c>
       <c r="S170" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="171" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="171" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B171">
         <v>11902106</v>
@@ -11232,40 +8853,35 @@
         <v>116</v>
       </c>
     </row>
-    <row r="172" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D172" t="s">
         <v>23</v>
       </c>
       <c r="E172" t="s">
-        <v>528</v>
+        <v>524</v>
+      </c>
+      <c r="I172" t="s">
+        <v>34</v>
       </c>
       <c r="Q172" t="s">
         <v>26</v>
       </c>
       <c r="S172" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="T172" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="U172" t="s">
         <v>304</v>
       </c>
-      <c r="V172" t="e">
-        <f>_xlfn.XLOOKUP(A172,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W172" t="e">
-        <f>_xlfn.XLOOKUP(A172,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="173" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="173" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B173">
         <v>12002568</v>
@@ -11298,12 +8914,12 @@
         <v>34</v>
       </c>
       <c r="S173" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="174" spans="1:23" x14ac:dyDescent="0.15">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="174" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B174">
         <v>11800343</v>
@@ -11324,7 +8940,7 @@
         <v>34</v>
       </c>
       <c r="O174" t="s">
-        <v>493</v>
+        <v>542</v>
       </c>
       <c r="P174" t="s">
         <v>37</v>
@@ -11336,12 +8952,12 @@
         <v>34</v>
       </c>
       <c r="S174" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="175" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="175" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B175">
         <v>12002565</v>
@@ -11368,7 +8984,7 @@
         <v>50</v>
       </c>
       <c r="O175" t="s">
-        <v>496</v>
+        <v>541</v>
       </c>
       <c r="P175" t="s">
         <v>37</v>
@@ -11380,12 +8996,12 @@
         <v>34</v>
       </c>
       <c r="S175" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="176" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="176" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="B176">
         <v>12003783</v>
@@ -11420,18 +9036,10 @@
       <c r="S176" t="s">
         <v>259</v>
       </c>
-      <c r="V176" t="str">
-        <f>_xlfn.XLOOKUP(A176,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>研发治理部</v>
-      </c>
-      <c r="W176" t="str">
-        <f>_xlfn.XLOOKUP(A176,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>三快支持组</v>
-      </c>
-    </row>
-    <row r="177" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="177" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="B177">
         <v>12102524</v>
@@ -11464,12 +9072,12 @@
         <v>178</v>
       </c>
       <c r="S177" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="178" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="178" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B178">
         <v>12003932</v>
@@ -11514,12 +9122,12 @@
         <v>49</v>
       </c>
       <c r="S178" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="179" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="179" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="B179">
         <v>11100755</v>
@@ -11552,20 +9160,12 @@
         <v>85</v>
       </c>
       <c r="S179" t="s">
-        <v>503</v>
-      </c>
-      <c r="V179" t="str">
-        <f>_xlfn.XLOOKUP(A179,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>研发治理部</v>
-      </c>
-      <c r="W179" t="str">
-        <f>_xlfn.XLOOKUP(A179,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>测试部</v>
-      </c>
-    </row>
-    <row r="180" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="180" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="B180">
         <v>12003927</v>
@@ -11613,18 +9213,18 @@
         <v>49</v>
       </c>
       <c r="S180" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="181" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="181" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D181" t="s">
         <v>63</v>
       </c>
       <c r="E181" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="F181" t="s">
         <v>166</v>
@@ -11639,7 +9239,7 @@
         <v>367</v>
       </c>
       <c r="O181" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="P181" t="s">
         <v>67</v>
@@ -11651,20 +9251,12 @@
         <v>85</v>
       </c>
       <c r="S181" t="s">
-        <v>474</v>
-      </c>
-      <c r="V181" t="str">
-        <f>_xlfn.XLOOKUP(A181,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>外包</v>
-      </c>
-      <c r="W181" t="str">
-        <f>_xlfn.XLOOKUP(A181,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>外包</v>
-      </c>
-    </row>
-    <row r="182" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="182" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="B182">
         <v>11100885</v>
@@ -11700,12 +9292,12 @@
         <v>34</v>
       </c>
       <c r="S182" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="183" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="183" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="D183" t="s">
         <v>23</v>
@@ -11723,23 +9315,15 @@
         <v>103</v>
       </c>
       <c r="S183" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="U183" t="s">
         <v>105</v>
       </c>
-      <c r="V183" t="e">
-        <f>_xlfn.XLOOKUP(A183,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W183" t="e">
-        <f>_xlfn.XLOOKUP(A183,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="184" spans="1:23" x14ac:dyDescent="0.15">
+    </row>
+    <row r="184" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="D184" t="s">
         <v>23</v>
@@ -11760,23 +9344,15 @@
         <v>103</v>
       </c>
       <c r="S184" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="U184" t="s">
         <v>105</v>
       </c>
-      <c r="V184" t="e">
-        <f>_xlfn.XLOOKUP(A184,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W184" t="e">
-        <f>_xlfn.XLOOKUP(A184,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="185" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="185" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="B185">
         <v>11000585</v>
@@ -11824,12 +9400,12 @@
         <v>34</v>
       </c>
       <c r="S185" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="186" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="186" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="C186" t="s">
         <v>64</v>
@@ -11861,18 +9437,10 @@
       <c r="S186" t="s">
         <v>97</v>
       </c>
-      <c r="V186" t="str">
-        <f>_xlfn.XLOOKUP(A186,[1]花名册!$A:$A,[1]花名册!$E:$E)</f>
-        <v>华南开发一组</v>
-      </c>
-      <c r="W186">
-        <f>_xlfn.XLOOKUP(A186,[1]花名册!$A:$A,[1]花名册!$F:$F)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="187" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="187" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="B187">
         <v>12002569</v>
@@ -11917,12 +9485,12 @@
         <v>34</v>
       </c>
       <c r="S187" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="188" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="188" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="B188">
         <v>12003773</v>
@@ -11973,9 +9541,9 @@
         <v>259</v>
       </c>
     </row>
-    <row r="189" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="D189" t="s">
         <v>23</v>
@@ -11993,7 +9561,7 @@
         <v>49</v>
       </c>
       <c r="O189" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="Q189" t="s">
         <v>26</v>
@@ -12005,12 +9573,12 @@
         <v>221</v>
       </c>
       <c r="T189" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="190" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="190" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="D190" t="s">
         <v>63</v>
@@ -12040,12 +9608,12 @@
         <v>46175</v>
       </c>
     </row>
-    <row r="191" spans="1:23" ht="14.25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="7" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="D191" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="E191" t="s">
         <v>31</v>
@@ -12069,15 +9637,15 @@
         <v>46175</v>
       </c>
     </row>
-    <row r="192" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="5" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="D192" t="s">
         <v>63</v>
       </c>
       <c r="E192" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="F192" t="s">
         <v>129</v>
@@ -12098,12 +9666,12 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="193" spans="1:20" hidden="1" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="5" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="D193" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="E193" t="s">
         <v>31</v>
@@ -12127,18 +9695,18 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="194" spans="1:20" hidden="1" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="5" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="D194" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="E194" t="s">
         <v>31</v>
       </c>
       <c r="F194" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="I194" t="s">
         <v>178</v>
@@ -12156,12 +9724,12 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="195" spans="1:20" hidden="1" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="11" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="D195" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="E195" t="s">
         <v>31</v>
@@ -12190,13 +9758,10 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:U195" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="4">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="5">
-      <filters blank="1"/>
+    <filterColumn colId="20">
+      <filters>
+        <filter val="异常未填"/>
+      </filters>
     </filterColumn>
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
